--- a/data/ams_weekly_data/White_Mulberry/ads_report_week26.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week26.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4786,4 +4787,890 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Portfolio name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Campaign Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Advertised ASIN</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Impressions</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Clicks</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Spend</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>14 Day Total Sales (₹)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>14 Day Total Units (#)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Camb Gaming Desk-B0CPFS24ML-BM-Product Collection-SB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7033</v>
+      </c>
+      <c r="E2" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2" t="n">
+        <v>794.0966666666667</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Camb Gaming Desk-B0CPFS24ML-BM-Product Collection-SB</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7033</v>
+      </c>
+      <c r="E3" t="n">
+        <v>93</v>
+      </c>
+      <c r="F3" t="n">
+        <v>794.0966666666667</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Camb Gaming Desk-B0CPFS24ML-BM-Product Collection-SB</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>7033</v>
+      </c>
+      <c r="E4" t="n">
+        <v>93</v>
+      </c>
+      <c r="F4" t="n">
+        <v>794.0966666666667</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3759</v>
+      </c>
+      <c r="E5" t="n">
+        <v>124</v>
+      </c>
+      <c r="F5" t="n">
+        <v>402.1585615143471</v>
+      </c>
+      <c r="G5" t="n">
+        <v>11838.52958220304</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7744</v>
+      </c>
+      <c r="E6" t="n">
+        <v>256</v>
+      </c>
+      <c r="F6" t="n">
+        <v>828.401438485653</v>
+      </c>
+      <c r="G6" t="n">
+        <v>24386.04041779696</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>9620</v>
+      </c>
+      <c r="E7" t="n">
+        <v>181</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1398.35</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7287.29</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>B0BFVMDJ2K</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>6621</v>
+      </c>
+      <c r="E8" t="n">
+        <v>119</v>
+      </c>
+      <c r="F8" t="n">
+        <v>737.2066666666666</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B0BFVNS8HS</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>6621</v>
+      </c>
+      <c r="E9" t="n">
+        <v>119</v>
+      </c>
+      <c r="F9" t="n">
+        <v>737.2066666666666</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SB-L shape-Multi Asin- KT- phrase</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>B0BFWD6SNF</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>6621</v>
+      </c>
+      <c r="E10" t="n">
+        <v>119</v>
+      </c>
+      <c r="F10" t="n">
+        <v>737.2066666666666</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SBV_B0CPFS24ML_Keyword_BMC</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12858</v>
+      </c>
+      <c r="E11" t="n">
+        <v>68</v>
+      </c>
+      <c r="F11" t="n">
+        <v>451.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4507</v>
+      </c>
+      <c r="E12" t="n">
+        <v>49</v>
+      </c>
+      <c r="F12" t="n">
+        <v>543.52</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>WM- SBV-Wall Mounted Stand- B0DP2WC5VW- Phrase &amp; exact</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B0DP2WC5VW</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7943</v>
+      </c>
+      <c r="E13" t="n">
+        <v>178</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1624.09</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2965.25</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-B0DB5VG39T - CT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3699</v>
+      </c>
+      <c r="E14" t="n">
+        <v>43</v>
+      </c>
+      <c r="F14" t="n">
+        <v>557.49</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2446.61</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>14</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B0DB5W4TCP</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>14</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B0DB5YTQZV</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>14</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>14</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>WM-SB-Monitor Arms-Branded</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>14</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>9050</v>
+      </c>
+      <c r="E21" t="n">
+        <v>93</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1610.590398675721</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6988.98</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B0DB5VVPSB</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>4717</v>
+      </c>
+      <c r="E22" t="n">
+        <v>49</v>
+      </c>
+      <c r="F22" t="n">
+        <v>839.569601324279</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3643.22</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>White Mulberry 10-Step Height Adjustable-B0DP2Z5DQ9-PT-KT-SBVV</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>B0DP2Z5DQ9</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>19203</v>
+      </c>
+      <c r="E23" t="n">
+        <v>93</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1404.97</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2372.03</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>B0CPFS24ML</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11324</v>
+      </c>
+      <c r="E24" t="n">
+        <v>113</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1165.481539214974</v>
+      </c>
+      <c r="G24" t="n">
+        <v>8999.783596790658</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-CT-SBV</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>B0DP32F346</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>4081</v>
+      </c>
+      <c r="E25" t="n">
+        <v>41</v>
+      </c>
+      <c r="F25" t="n">
+        <v>420.0284607850257</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3243.436403209341</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>White Mulberry Monitor Arm-B0DB5VG39T-PT-KT-SBV</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>B0DB5VG39T</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10853</v>
+      </c>
+      <c r="E26" t="n">
+        <v>115</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1895.82</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2329.66</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>White Mulberry</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>